--- a/docs/recipe-management.xlsx
+++ b/docs/recipe-management.xlsx
@@ -3185,7 +3185,1205 @@
         </is>
       </c>
     </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">manual-img-2092-carrot-cake</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">キャロットケーキ</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">review</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">assets/processed-images/IMG_2092.HEIC.png</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">卵 2個
+砂糖 160g
+人参 220g（すりおろし）
+油 120g
+薄力粉 180g
+重そう 小さじ1
+ベーキングパウダー 小さじ1.5
+シナモン 小さじ1
+生クリーム 適量
+レモンパウダー 適量</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">卵を卵白と卵黄に分ける
+卵白をボールでメレンゲにし、ぽってりしてきたら卵黄を入れる
+砂糖を3回に分けて入れ、白くもったりするまでよく混ぜる
+油を少しずつ入れながらしっかり混ぜ、すりおろした人参を加えて混ぜる
+薄力粉、重そう、ベーキングパウダー、シナモンを合わせてふるっておき、加えてさっくり混ぜる
+中フライパンにクッキングシートを敷いて生地を流し入れ、プレートモード170度で40分焼く
+しっかり冷まし、生クリームとレモンパウダーで作ったレモンクリームを上にのせて完成</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-06-06T00:00:00+09:00</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-06-06T00:00:00+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">manual-img-2093-pear-compote</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">洋梨コンポート</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">review</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">assets/processed-images/IMG_2093.HEIC.png</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">洋梨
+水 100ml
+酒 大さじ5
+砂糖 大さじ5
+りんご酢 適量
+レモン汁またはレモンパウダー 適量
+塩 適量</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">砂糖が溶けてから洋梨を投入して煮込む
+りんご酢、レモン汁またはレモンパウダー、塩は味を引き出す程度に随時加えて調整する
+ミントシロップを作る場合は湯を沸かしてミントを投入し、インダクションレンジのモード5で2分加熱し、その後30分以上蒸らす
+レモンにはちみつを入れて煮たものを冷めた状態で合わせてもよい</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ミントシロップは、はちみつ、水、ミントのメモあり。</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-06-06T00:05:00+09:00</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-06-06T00:05:00+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">manual-img-2093-sesame-anko</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ごまあんこ</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">review</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">assets/processed-images/IMG_2093.HEIC.png</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">あんこ 200g
+黒ごまペースト 20〜30g
+ごま油 小さじ1</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">材料を全てなべに入れて練り上げる
+弱〜中火で加熱し、水分が必要な場合は適宜入れて調整する</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-06-06T00:05:00+09:00</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-06-06T00:05:00+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">manual-img-2093-azuki-an</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">小豆あん</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">review</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">assets/processed-images/IMG_2093.HEIC.png</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">小豆 200g
+砂糖 200g
+塩 ひとつまみ
+水 適量</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">小豆を軽く水洗いする
+小豆と小豆の4倍程度の熱湯を鍋に入れてゆでる
+蒸気が上がったら湯を捨て、豆を水にさらす
+再び鍋で豆と4倍の水を新たに入れ、40分〜1時間煮て豆を柔らかくする
+柔らかくなったら大半の湯を捨て、砂糖を3回くらいに分けて鍋に加える
+塩も入れ、好みの固さまで練り上げる
+つぶしあんにする場合は湯を捨ててからフープロで砕き、なべに戻して砂糖と塩を入れる</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-06-06T00:05:00+09:00</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-06-06T00:05:00+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">manual-img-2094-honey-ginger-cookie</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">はちみつしょうがクッキー</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">review</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">assets/processed-images/IMG_2094.HEIC.png</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">薄力粉 80g
+エサンテ 50g
+砂糖 15g
+しょうがはちみつ漬け 40g
+いりごま 大さじ1</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ボールに全ての材料を入れてまとめ、棒状にする
+ラップにくるんで冷蔵庫または冷凍庫で固める
+1cmくらいにスライスして180度で15分焼く</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">しょうがははちみつに一日くらい漬けておく。水気を切らなくてもよい旨のメモあり。</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-06-06T00:10:00+09:00</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-06-06T00:10:00+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">manual-img-2094-yaki-sakura-mochi</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">焼き桜餅</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">review</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">assets/processed-images/IMG_2094.HEIC.png</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">食紅 赤色 適量
+白玉粉 25g
+砂糖 30g
+塩 2g
+薄力粉 100g
+水 150cc
+あんこ 300g
+桜の葉塩漬け 10枚</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">桜の葉塩漬けを20分くらい水につけて塩抜きする
+あんこ以外の材料を全て混ぜ、一晩寝かす
+薄く生地を敷いて焼く
+あんこを包み、桜の葉を巻いて完成</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10個分。焼くときは油を敷く旨のメモあり。</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-06-06T00:10:00+09:00</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-06-06T00:10:00+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">manual-img-2095-three-cookie</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">スリークッキー</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">review</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">assets/processed-images/IMG_2095.HEIC.png</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">小麦粉 万能カップ2
+コーンスターチ 万能カップ2
+粉砂糖 万能カップ1
+ナッツつぶす 万能カップ2
+バターまたはエサンテ 100g
+バニラオイル 小さじ2</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">材料を全て混ぜて固める
+丸めて、クッキングシートを敷いた大フライパンに並べる
+ケーキモード強で焼く
+焼きあがったらすぐに取り出して冷ます
+冷めたら粉砂糖をふる</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ほろほろサクサクとのメモあり。</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-06-06T00:15:00+09:00</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-06-06T00:15:00+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">manual-img-2095-ginger-syrup</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ジンジャーシロップ</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">review</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">assets/processed-images/IMG_2095.HEIC.png</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">生姜 150〜160g
+砂糖 150g
+水 500ml
+ローリエ 2枚
+ブラックペッパーホール 12粒
+クエン酸 小さじ1/2
+ペパーミント 適量
+はちみつ 適量</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">材料を煮る
+ペパーミントは沸騰したら入れて、すぐ取り出す</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">クエン酸はレモンの代用として使う旨のメモあり。</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-06-06T00:15:00+09:00</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-06-06T00:15:00+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">manual-img-2096-big-steamed-bread</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ドデカ蒸しパン</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">review</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">assets/processed-images/IMG_2096.HEIC.png</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">小麦粉 300g
+黒砂糖 300g
+卵 3個
+重そう 大さじ1
+牛乳または甘酒 250cc
+はちみつまたはメープルシロップ 大さじ3
+お酢 適量
+好みでレーズンなど</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">粉類、黒砂糖、卵、重そうをざっくり混ぜ合わせる
+牛乳または甘酒、はちみつまたはメープルシロップを入れて混ぜる
+全体が混ざったらお酢を入れて混ぜる
+ウォック鍋に2カップの水を入れて網ラックをのせ、市販のクッキングシートをクロスさせるように斜めにのせる
+生地を流し入れ、好みでレーズンなどをふりかける
+インダクションレンジ6〜7で30分蒸す</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-06-06T00:20:00+09:00</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-06-06T00:20:00+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">manual-img-2096-microwave-brownie</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">レンジだけでブラウニー</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">review</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">assets/processed-images/IMG_2096.HEIC.png</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">板チョコ 2枚（100g）
+無塩バター 50g
+砂糖 大さじ1
+卵 1個
+ホットケーキミックス 大さじ5</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">耐熱ボールに割ったチョコと無塩バターを入れ、レンジ700Wで1分加熱する
+砂糖と卵を加えて混ぜる
+ホットケーキミックスを加えて混ぜる
+15cm角の容器にクッキングシートを敷き、生地を流し入れて空気を抜く
+好みでクルミやクッキーをのせる
+ラップをせずにレンジ弱で2分半加熱する</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12分でできる旨のメモあり。</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-06-06T00:20:00+09:00</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-06-06T00:20:00+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">manual-img-2097-custard-cream</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">カスタードクリーム</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">review</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">assets/processed-images/IMG_2097.HEIC.png</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">卵黄のみ Mサイズ1個分
+砂糖 15g
+コーンスターチ 8g
+バニラオイル 少々
+牛乳 100g
+エサンテ 12g</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">砂糖とコーンスターチをホイッパーでよく混ぜ合わせる
+卵黄を加えて白っぽくなるまでホイップする
+牛乳を3回に分けて加え、その都度ホイッパーでよく混ぜる
+ラップをして500Wで2分加熱する
+端の方から固まったクリームをよく混ぜ、均一なクリーム状にする
+ゴムベラで整える
+再度ラップをして500Wで1分加熱する
+ふつふつしたことを確認してホイッパーでよく混ぜる
+密着するようにラップをして氷水にあててしっかり冷やす
+しっかり冷えたらゴムベラでなめらかになるよう混ぜる</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">分量によって加熱時間が変わる。3倍量の場合は1回目7分、2回目2分のメモあり。</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-06-06T00:30:00+09:00</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-06-06T00:30:00+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">manual-img-2097-maple-walnuts</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">メープルくるみ</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">review</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">assets/processed-images/IMG_2097.HEIC.png</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">くるみ 80g
+メープルシロップ 大さじ3
+塩 ひとつまみ</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フライパンでくるみを油なしの弱火で炒る
+焼き色がついたら火を止める
+くるみをフライパンの周りに寄せて中心を空け、真ん中にメープルシロップと塩を入れて弱火で沸騰させる
+沸騰したらくるみも混ぜる
+くるみにシロップが絡んだら一旦火を止める
+火を止めたままポロポロになるまで混ぜる
+一つ一つがくっつかなくなったら皿の上で冷ます</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">くるみは好きな大きさに割る。</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-06-06T00:30:00+09:00</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-06-06T00:30:00+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">manual-img-2098-tofu-cocoa-steamed-cake</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">豆腐とココアのしっとり蒸しケーキ</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">review</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">assets/processed-images/IMG_2098.HEIC.png</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">豆腐 1丁（300g使用）
+卵 5個
+砂糖 80g
+米粉 60g
+ベーキングパウダー 8g
+ココア 45g
+好みでくるみやアーモンド</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">豆腐をホイッパーやブレンダーでしっかり混ぜてペースト状にする
+ほかの材料を順に入れてさらに混ぜる
+タッパにクッキングシートを敷き、生地を入れてタッパに刺激を与えて空気を抜く
+上にナッツなどをまんべんなくのせる
+レンジ600Wで5分加熱し、中心が生になりがちなので追加で1分30秒〜2分ほど加熱する
+できたらクッキングシートから外して冷ます
+最後に溶けにくい粉砂糖を茶こしでかけて完成</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">タッパ2つ分。おからパウダー、きび糖、小袋のベーキングパウダー2袋、バンホーテンココアのメモあり。加熱目安は6分30秒。</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-06-06T00:35:00+09:00</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-06-06T00:35:00+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">manual-img-2098-milk-kanten</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">牛乳寒天</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">review</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">assets/processed-images/IMG_2098.HEIC.png</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">寒天 5g
+湯 200ml
+牛乳 400ml
+砂糖 60g</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">材料を煮詰める
+固めて完成</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">棒寒天の場合は水で予め30分戻して固く絞る。</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-06-06T00:35:00+09:00</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-06-06T00:35:00+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">manual-img-2099-poached-egg</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ポーチドエッグ</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">review</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">assets/processed-images/IMG_2099.HEIC.png</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">卵 1個
+水 3カップ
+酢 大さじ1
+塩 少々</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">水、酢、塩を沸かして湯を混ぜ、渦を作る
+卵を静かに入れる
+弱火で90秒たったらすくい上げる</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-06-06T00:40:00+09:00</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-06-06T00:40:00+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">manual-img-2099-hollandaise-sauce</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">オランデーソース</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">review</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">assets/processed-images/IMG_2099.HEIC.png</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">卵黄 1個分
+レモン汁 小さじ1
+マーガリン 大さじ1
+マヨネーズ 大さじ1
+黒こしょう 少々</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">卵黄だけをまず混ぜる
+そのほかの材料を入れて混ぜる
+レモン汁を少し濃いめに入れて混ぜる</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-06-06T00:40:00+09:00</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-06-06T00:40:00+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">manual-img-2099-coleslaw</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">コールスロー</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">review</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">assets/processed-images/IMG_2099.HEIC.png</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">キャベツ
+コーン
+ベーコンまたはハム
+マヨネーズ 大さじ3
+酢 大さじ1.5
+砂糖 小さじ1</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">材料を混ぜ合わせて完成</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-06-06T00:40:00+09:00</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-06-06T00:40:00+09:00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L44"/>
+  <autoFilter ref="A1:L61"/>
 </worksheet>
 </file>